--- a/downloads/gas-data-analysis-1404.xlsx
+++ b/downloads/gas-data-analysis-1404.xlsx
@@ -1183,13 +1183,13 @@
       <c r="J2" s="7" t="n">
         <v>47.9</v>
       </c>
-      <c r="K2" s="7" t="n">
+      <c r="K2" s="9" t="n">
         <v>6</v>
       </c>
       <c r="L2" s="7" t="n">
         <v>3.33</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="M2" s="9" t="n">
         <v>17</v>
       </c>
       <c r="N2" s="7" t="n">
@@ -1238,13 +1238,13 @@
       <c r="L3" s="7" t="n">
         <v>6.34</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M3" s="9" t="n">
         <v>16</v>
       </c>
       <c r="N3" s="7" t="n">
         <v>31.55</v>
       </c>
-      <c r="O3" s="7" t="n">
+      <c r="O3" s="9" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       <c r="J6" s="7" t="n">
         <v>56.56</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="K6" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L6" s="7" t="n">
@@ -1434,7 +1434,7 @@
       <c r="L7" s="7" t="n">
         <v>1.64</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="9" t="n">
         <v>13</v>
       </c>
       <c r="N7" s="7" t="n">
@@ -1529,10 +1529,10 @@
       <c r="K9" s="7" t="n">
         <v>2.7</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="L9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="9" t="n">
         <v>12</v>
       </c>
       <c r="N9" s="7" t="n">
@@ -1601,7 +1601,7 @@
         <v>36.77</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>12.03</v>
+        <v>12.02</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>18.52</v>
@@ -1722,13 +1722,13 @@
       <c r="J13" s="7" t="n">
         <v>64.5</v>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="K13" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L13" s="7" t="n">
         <v>3.33</v>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="9" t="n">
         <v>17</v>
       </c>
       <c r="N13" s="7" t="n">
@@ -1771,13 +1771,13 @@
       <c r="J14" s="7" t="n">
         <v>66.13</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="K14" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="7" t="n">
         <v>6.67</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="9" t="n">
         <v>18</v>
       </c>
       <c r="N14" s="7" t="n">
@@ -1823,7 +1823,7 @@
       <c r="K15" s="7" t="n">
         <v>2.1</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="L15" s="9" t="n">
         <v>3</v>
       </c>
       <c r="M15" s="7" t="n">
@@ -1869,7 +1869,7 @@
       <c r="J16" s="7" t="n">
         <v>67.47</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="7" t="n">
@@ -1944,7 +1944,7 @@
         <v>29.46</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>8.81</v>
+        <v>8.82</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>22.87</v>
@@ -1973,7 +1973,7 @@
       <c r="L18" s="7" t="n">
         <v>3.43</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="9" t="n">
         <v>14</v>
       </c>
       <c r="N18" s="7" t="n">
@@ -1989,7 +1989,7 @@
           <t>قزوین</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="9" t="n">
         <v>29</v>
       </c>
       <c r="C19" s="7" t="n">
@@ -2013,7 +2013,7 @@
       <c r="I19" s="7" t="n">
         <v>87.3</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="9" t="n">
         <v>71</v>
       </c>
       <c r="K19" s="7" t="n">
@@ -2166,7 +2166,7 @@
       <c r="K22" s="7" t="n">
         <v>1.8</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="L22" s="9" t="n">
         <v>9</v>
       </c>
       <c r="M22" s="7" t="n">
@@ -2189,7 +2189,7 @@
         <v>23.98</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>5.6</v>
+        <v>5.59</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>30.94</v>
@@ -2215,7 +2215,7 @@
       <c r="K23" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="L23" s="9" t="n">
         <v>7</v>
       </c>
       <c r="M23" s="7" t="n">
@@ -2261,7 +2261,7 @@
       <c r="J24" s="7" t="n">
         <v>76.5</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K24" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L24" s="7" t="n">
@@ -2287,7 +2287,7 @@
         <v>23.48</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>6.4</v>
+        <v>6.39</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>25.85</v>
@@ -2316,7 +2316,7 @@
       <c r="L25" s="7" t="n">
         <v>5.33</v>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="9" t="n">
         <v>18</v>
       </c>
       <c r="N25" s="7" t="n">
@@ -2411,7 +2411,7 @@
       <c r="K27" s="7" t="n">
         <v>1.4</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="L27" s="9" t="n">
         <v>7</v>
       </c>
       <c r="M27" s="7" t="n">
@@ -2509,10 +2509,10 @@
       <c r="K29" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="L29" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="9" t="n">
         <v>17</v>
       </c>
       <c r="N29" s="7" t="n">
@@ -2531,7 +2531,7 @@
       <c r="B30" s="7" t="n">
         <v>16.72</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="9" t="n">
         <v>4</v>
       </c>
       <c r="D30" s="7" t="n">
@@ -2655,7 +2655,7 @@
         <v>0.7</v>
       </c>
       <c r="L32" s="9" t="n"/>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="9" t="n">
         <v>27</v>
       </c>
       <c r="N32" s="7" t="n">
@@ -2881,7 +2881,7 @@
       <c r="L2" s="7" t="n">
         <v>0.9</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="M2" s="9" t="n">
         <v>3</v>
       </c>
       <c r="N2" s="7" t="n">
@@ -2915,7 +2915,7 @@
       <c r="H3" s="7" t="n">
         <v>4.3</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="9" t="n">
         <v>3</v>
       </c>
       <c r="J3" s="7" t="n">
@@ -2924,10 +2924,10 @@
       <c r="K3" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="L3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M3" s="9" t="n">
         <v>3</v>
       </c>
       <c r="N3" s="7" t="n">
@@ -2992,7 +2992,7 @@
       <c r="C5" s="7" t="n">
         <v>26.4</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="9" t="n">
         <v>15</v>
       </c>
       <c r="E5" s="7" t="n">
@@ -3004,10 +3004,10 @@
       <c r="G5" s="7" t="n">
         <v>4.6</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J5" s="7" t="n">
@@ -3019,7 +3019,7 @@
       <c r="L5" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="9" t="n">
         <v>2</v>
       </c>
       <c r="N5" s="7" t="n">
@@ -3032,7 +3032,7 @@
           <t>البرز</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="9" t="n">
         <v>32</v>
       </c>
       <c r="C6" s="7" t="n">
@@ -3041,7 +3041,7 @@
       <c r="D6" s="7" t="n">
         <v>15.1</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="9" t="n">
         <v>8</v>
       </c>
       <c r="F6" s="7" t="n">
@@ -3056,7 +3056,7 @@
       <c r="I6" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="7" t="n">
@@ -3142,7 +3142,7 @@
       <c r="G8" s="7" t="n">
         <v>1.8</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="7" t="n">
@@ -3182,7 +3182,7 @@
       <c r="E9" s="7" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="9" t="n">
         <v>5</v>
       </c>
       <c r="G9" s="7" t="n">
@@ -3197,13 +3197,13 @@
       <c r="J9" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="K9" s="7" t="n">
+      <c r="K9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="9" t="n">
         <v>4</v>
       </c>
       <c r="N9" s="7" t="n">
@@ -3216,7 +3216,7 @@
           <t>چهارمحال و بختیاری</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="9" t="n">
         <v>21</v>
       </c>
       <c r="C10" s="7" t="n">
@@ -3249,7 +3249,7 @@
       <c r="L10" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="9" t="n">
         <v>2</v>
       </c>
       <c r="N10" s="7" t="n">
@@ -3265,7 +3265,7 @@
       <c r="B11" s="7" t="n">
         <v>43.6</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="7" t="n">
@@ -3329,7 +3329,7 @@
       <c r="H12" s="7" t="n">
         <v>1.6</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="7" t="n">
@@ -3372,7 +3372,7 @@
       <c r="G13" s="7" t="n">
         <v>4.7</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="9" t="n">
         <v>3</v>
       </c>
       <c r="I13" s="7" t="n">
@@ -3403,10 +3403,10 @@
       <c r="B14" s="7" t="n">
         <v>31.1</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="9" t="n">
         <v>16</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -3602,7 +3602,7 @@
       <c r="G18" s="7" t="n">
         <v>3.3</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I18" s="7" t="n">
@@ -3654,7 +3654,7 @@
       <c r="I19" s="7" t="n">
         <v>1.4</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="7" t="n">
@@ -3795,7 +3795,7 @@
       <c r="J22" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="K22" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L22" s="7" t="n">
@@ -3838,7 +3838,7 @@
       <c r="I23" s="7" t="n">
         <v>1.8</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="7" t="n">
@@ -3887,7 +3887,7 @@
       <c r="J24" s="7" t="n">
         <v>3.2</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K24" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="7" t="n">
@@ -3930,7 +3930,7 @@
       <c r="I25" s="7" t="n">
         <v>1.7</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="J25" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="7" t="n">
@@ -4007,7 +4007,7 @@
       <c r="D27" s="7" t="n">
         <v>15.8</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="9" t="n">
         <v>11</v>
       </c>
       <c r="F27" s="7" t="n">
@@ -4019,13 +4019,13 @@
       <c r="H27" s="7" t="n">
         <v>3.2</v>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="I27" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J27" s="7" t="n">
         <v>1.4</v>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="K27" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="7" t="n">
@@ -4301,7 +4301,7 @@
       <c r="J33" s="11" t="n">
         <v>1.4</v>
       </c>
-      <c r="K33" s="11" t="n">
+      <c r="K33" s="13" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="11" t="n">
@@ -4452,7 +4452,7 @@
       <c r="G2" s="7" t="n">
         <v>3.1</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="H2" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I2" s="7" t="n">
@@ -4694,7 +4694,7 @@
       <c r="K7" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="7" t="n">
@@ -4716,7 +4716,7 @@
       <c r="C8" s="7" t="n">
         <v>12.9</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="9" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -4734,16 +4734,16 @@
       <c r="I8" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="L8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="7" t="n">
@@ -4756,7 +4756,7 @@
           <t>تهران</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="9" t="n">
         <v>57</v>
       </c>
       <c r="C9" s="7" t="n">
@@ -4771,7 +4771,7 @@
       <c r="F9" s="7" t="n">
         <v>1.9</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="7" t="n">
@@ -4878,7 +4878,7 @@
       <c r="K11" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="7" t="n">
@@ -5001,7 +5001,7 @@
       <c r="F14" s="7" t="n">
         <v>1.8</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="7" t="n">
@@ -5182,7 +5182,7 @@
       <c r="E18" s="7" t="n">
         <v>3.9</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G18" s="7" t="n">
@@ -5228,7 +5228,7 @@
       <c r="E19" s="7" t="n">
         <v>5.6</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="9" t="n">
         <v>3</v>
       </c>
       <c r="G19" s="7" t="n">
@@ -5372,7 +5372,7 @@
       <c r="G22" s="7" t="n">
         <v>1.6</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="7" t="n">
@@ -5421,7 +5421,7 @@
       <c r="H23" s="7" t="n">
         <v>1.6</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="7" t="n">
@@ -5688,7 +5688,7 @@
       <c r="E29" s="7" t="n">
         <v>4.9</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="9" t="n">
         <v>3</v>
       </c>
       <c r="G29" s="7" t="n">
@@ -5722,7 +5722,7 @@
           <t>هرمزگان</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="B30" s="9" t="n">
         <v>89</v>
       </c>
       <c r="C30" s="7" t="n">
@@ -5746,16 +5746,16 @@
       <c r="I30" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="J30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="7" t="n">
+      <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="L30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="7" t="n">
@@ -5786,7 +5786,7 @@
       <c r="G31" s="7" t="n">
         <v>3.1</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="H31" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I31" s="7" t="n">
@@ -5826,7 +5826,7 @@
       <c r="E32" s="7" t="n">
         <v>3.6</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G32" s="7" t="n">
@@ -5875,7 +5875,7 @@
       <c r="F33" s="11" t="n">
         <v>3.3</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="G33" s="13" t="n">
         <v>2</v>
       </c>
       <c r="H33" s="11" t="n">
@@ -6036,13 +6036,13 @@
       <c r="C3" s="7" t="n">
         <v>26.6</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="9" t="n">
         <v>55</v>
       </c>
       <c r="G3" s="7" t="n">
@@ -6067,13 +6067,13 @@
       <c r="B4" s="7" t="n">
         <v>46.7</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>22.3</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="7" t="n">
@@ -6135,7 +6135,7 @@
       <c r="B6" s="7" t="n">
         <v>52.2</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D6" s="7" t="n">
@@ -6240,10 +6240,10 @@
       <c r="C9" s="7" t="n">
         <v>22.7</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="7" t="n">
@@ -6255,7 +6255,7 @@
       <c r="H9" s="7" t="n">
         <v>10.8</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="9" t="n">
         <v>3</v>
       </c>
       <c r="J9" s="8" t="n">
@@ -6345,7 +6345,7 @@
       <c r="D12" s="7" t="n">
         <v>19.82</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="7" t="n">
@@ -6357,7 +6357,7 @@
       <c r="H12" s="7" t="n">
         <v>10.21</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J12" s="8" t="n">
@@ -6379,7 +6379,7 @@
       <c r="D13" s="7" t="n">
         <v>22.2</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F13" s="7" t="n">
@@ -6481,7 +6481,7 @@
       <c r="D16" s="7" t="n">
         <v>20.92</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F16" s="7" t="n">
@@ -6490,7 +6490,7 @@
       <c r="G16" s="7" t="n">
         <v>16.4</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="9" t="n">
         <v>9</v>
       </c>
       <c r="I16" s="7" t="n">
@@ -6546,7 +6546,7 @@
       <c r="C18" s="7" t="n">
         <v>26.8</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="9" t="n">
         <v>27</v>
       </c>
       <c r="E18" s="7" t="n">
@@ -6555,7 +6555,7 @@
       <c r="F18" s="7" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="9" t="n">
         <v>19</v>
       </c>
       <c r="H18" s="7" t="n">
@@ -6592,7 +6592,7 @@
       <c r="G19" s="7" t="n">
         <v>20.3</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="9" t="n">
         <v>11</v>
       </c>
       <c r="I19" s="7" t="n">
@@ -6648,7 +6648,7 @@
       <c r="C21" s="7" t="n">
         <v>27.1</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="9" t="n">
         <v>25</v>
       </c>
       <c r="E21" s="7" t="n">
@@ -6685,7 +6685,7 @@
       <c r="D22" s="7" t="n">
         <v>21.28</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F22" s="7" t="n">
@@ -6759,7 +6759,7 @@
       <c r="F24" s="7" t="n">
         <v>62.6</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="9" t="n">
         <v>21</v>
       </c>
       <c r="H24" s="7" t="n">
@@ -6787,7 +6787,7 @@
       <c r="D25" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
       <c r="F25" s="7" t="n">
@@ -6799,7 +6799,7 @@
       <c r="H25" s="7" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I25" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J25" s="8" t="n">
@@ -6861,7 +6861,7 @@
       <c r="F27" s="7" t="n">
         <v>61.3</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="9" t="n">
         <v>23</v>
       </c>
       <c r="H27" s="7" t="n">
@@ -6914,7 +6914,7 @@
           <t>مرکزی</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="9" t="n">
         <v>48</v>
       </c>
       <c r="C29" s="7" t="n">
@@ -6985,7 +6985,7 @@
       <c r="B31" s="7" t="n">
         <v>45.1</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D31" s="7" t="n">
@@ -7232,7 +7232,7 @@
       <c r="D3" s="7" t="n">
         <v>10.91</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F3" s="7" t="n">
@@ -7312,7 +7312,7 @@
       <c r="B5" s="7" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="9" t="n">
         <v>22</v>
       </c>
       <c r="D5" s="7" t="n">
@@ -7361,7 +7361,7 @@
       <c r="D6" s="7" t="n">
         <v>4.9</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="7" t="n">
@@ -7413,7 +7413,7 @@
       <c r="G7" s="7" t="n">
         <v>5.39</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="7" t="n">
@@ -7428,7 +7428,7 @@
       <c r="L7" s="17" t="n">
         <v>4.9</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="9" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7453,13 +7453,13 @@
       <c r="F8" s="7" t="n">
         <v>97.7</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="17" t="n">
@@ -7540,7 +7540,7 @@
       <c r="G10" s="7" t="n">
         <v>14.09</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="9" t="n">
         <v>4</v>
       </c>
       <c r="I10" s="7" t="n">
@@ -7555,7 +7555,7 @@
       <c r="L10" s="17" t="n">
         <v>2.23</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       <c r="L11" s="17" t="n">
         <v>4.14</v>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       <c r="D13" s="7" t="n">
         <v>7.01</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="7" t="n">
@@ -7755,7 +7755,7 @@
       <c r="G15" s="7" t="n">
         <v>14.6</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="9" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="7" t="n">
@@ -7786,7 +7786,7 @@
       <c r="C16" s="7" t="n">
         <v>17.4</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -7813,7 +7813,7 @@
       <c r="L16" s="17" t="n">
         <v>4.55</v>
       </c>
-      <c r="M16" s="17" t="n">
+      <c r="M16" s="9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7853,10 +7853,10 @@
       <c r="K17" s="17" t="n">
         <v>2.38</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="M17" s="17" t="n">
+      <c r="M17" s="9" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
           <t>قزوین</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="9" t="n">
         <v>71</v>
       </c>
       <c r="C19" s="7" t="n">
@@ -7983,7 +7983,7 @@
         <v>2.01</v>
       </c>
       <c r="L20" s="17" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="M20" s="17" t="n">
         <v>5.5</v>
@@ -8053,7 +8053,7 @@
       <c r="F22" s="7" t="n">
         <v>87.8</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="9" t="n">
         <v>9</v>
       </c>
       <c r="H22" s="7" t="n">
@@ -8114,7 +8114,7 @@
       <c r="L23" s="17" t="n">
         <v>1.75</v>
       </c>
-      <c r="M23" s="17" t="n">
+      <c r="M23" s="9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       <c r="G24" s="7" t="n">
         <v>11.11</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H24" s="9" t="n">
         <v>3</v>
       </c>
       <c r="I24" s="7" t="n">
@@ -8176,7 +8176,7 @@
       <c r="D25" s="7" t="n">
         <v>6.19</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F25" s="7" t="n">
@@ -8262,7 +8262,7 @@
       <c r="D27" s="7" t="n">
         <v>7.6</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F27" s="7" t="n">
@@ -8271,7 +8271,7 @@
       <c r="G27" s="7" t="n">
         <v>12.2</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="H27" s="9" t="n">
         <v>3</v>
       </c>
       <c r="I27" s="7" t="n">
@@ -8305,7 +8305,7 @@
       <c r="D28" s="7" t="n">
         <v>13.6</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
       <c r="F28" s="7" t="n">
@@ -8403,7 +8403,7 @@
       <c r="H30" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="17" t="n">
@@ -8412,7 +8412,7 @@
       <c r="K30" s="17" t="n">
         <v>5.12</v>
       </c>
-      <c r="L30" s="17" t="n">
+      <c r="L30" s="9" t="n">
         <v>9</v>
       </c>
       <c r="M30" s="9" t="n"/>
@@ -8438,7 +8438,7 @@
       <c r="F31" s="7" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="9" t="n">
         <v>15</v>
       </c>
       <c r="H31" s="7" t="n">

--- a/downloads/gas-data-analysis-1404.xlsx
+++ b/downloads/gas-data-analysis-1404.xlsx
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تحلیل مصرف گاز خانگی به تفکیک پله — سال ۱۴۰۴</t>
+          <t>تحلیل مصرف گاز خانگی ۱۴۰۴</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>مدیریت گازرسانی، امور تعرفه‌ها و قراردادها — شرکت ملی گاز ایران</t>
+          <t>مدیریت گازرسانی — امور تعرفه‌ها و قراردادها — شرکت ملی گاز ایران</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>۳۱ استان × ۱۲ پلهٔ دورهٔ سرد × ۴ پلهٔ دورهٔ گرم</t>
+          <t>۳۱ استان · ۱۲ پلهٔ دورهٔ سرد · ۴ پلهٔ دورهٔ گرم</t>
         </is>
       </c>
     </row>

--- a/downloads/gas-data-analysis-1404.xlsx
+++ b/downloads/gas-data-analysis-1404.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="دورهٔ گرم" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="گروه‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="منحنی لورنز" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مقایسهٔ جهانی" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تحلیل و راهکار" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +66,11 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -100,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,6 +159,13 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,6 +486,83 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>مصرف گاز خانگی به‌ازای هر نفر</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'مقایسهٔ جهانی'!$A$2:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'مقایسهٔ جهانی'!$B$2:$B$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -509,6 +600,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -8729,4 +8847,597 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>کشور</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>مقدار</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>سنجه</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>واحد</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>ایران</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>مصرف گاز خانگی به‌ازای هر نفر</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>مترمکعب در سال</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>روسیه</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>830</v>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>مصرف گاز خانگی به‌ازای هر نفر</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>مترمکعب در سال</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>ازبکستان</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>640</v>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>مصرف گاز خانگی به‌ازای هر نفر</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>مترمکعب در سال</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>ترکیه</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>330</v>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>مصرف گاز خانگی به‌ازای هر نفر</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>مترمکعب در سال</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>ایتالیا</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>310</v>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>مصرف گاز خانگی به‌ازای هر نفر</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>مترمکعب در سال</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>آلمان</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>290</v>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>مصرف گاز خانگی به‌ازای هر نفر</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>مترمکعب در سال</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>بریتانیا</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>280</v>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>مصرف گاز خانگی به‌ازای هر نفر</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>مترمکعب در سال</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>آمریکا</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>مصرف گاز خانگی به‌ازای هر نفر</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>مترمکعب در سال</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>چین</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>مصرف گاز خانگی به‌ازای هر نفر</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>مترمکعب در سال</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>ایران</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>یارانهٔ انرژی به‌عنوان درصدی از تولید ناخالص داخلی</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>الجزایر</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>یارانهٔ انرژی به‌عنوان درصدی از تولید ناخالص داخلی</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>یارانهٔ انرژی به‌عنوان درصدی از تولید ناخالص داخلی</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>عربستان</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>یارانهٔ انرژی به‌عنوان درصدی از تولید ناخالص داخلی</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>روسیه</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>یارانهٔ انرژی به‌عنوان درصدی از تولید ناخالص داخلی</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>هند</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>یارانهٔ انرژی به‌عنوان درصدی از تولید ناخالص داخلی</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>چین</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>یارانهٔ انرژی به‌عنوان درصدی از تولید ناخالص داخلی</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>درصد</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>ارقام مقایسه‌ای تقریبی و از گزارش‌های عمومی نهادهای بین‌المللی برگرفته شده‌اند. پیش از انتشار رسمی، با منبع مورد تأیید سازمان بازبینی و در همین پنل به‌روزرسانی شوند.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>بخش</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>عنوان</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>متن</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>تفسیر</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>این ارقام یعنی چه؟</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>اعداد فصل‌های پیشین یک الگوی آشنا را نشان می‌دهند: یارانهٔ انرژی که به‌صورت یکسان روی تعرفه سوار شده، در عمل نامتقارن توزیع می‌شود. هرچه مشترک بالاتر روی نردبان باشد، سهم بیشتری از این یارانه می‌برد — نه چون نیازمندتر است، بلکه چون بیشتر مصرف می‌کند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>تفسیر — نکته</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>یارانه با مصرف بالا می‌رود، نه با نیاز</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>دولت برای هر واحد گاز، صرف‌نظر از پلهٔ مصرف، یارانه می‌پردازد. نتیجه این است که ۱۴٫۴٪ از مشترکین که بالاتر از الگو مصرف می‌کنند، بزرگ‌ترین سهم مطلق یارانهٔ پنهان را دریافت می‌کنند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>تفسیر — نکته</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>سرما فقط بخشی از ماجراست</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>میانگین دمای استان تنها بخشی از پراکندگی مصرف مازاد را توضیح می‌دهد. باقی‌مانده را باید در عایق‌بندی ساختمان، سن وسایل گرمایشی، الگوی رفتاری خانوار و ضعف سیگنال قیمتی در پله‌های بالا جست‌وجو کرد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>تفسیر — نکته</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>شیب تعرفه در بالای نردبان کم‌جان است</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>وقتی فاصلهٔ قیمتی میان پله‌های بالا کم باشد، مشترک پرمصرف انگیزهٔ چندانی برای کاهش مصرف ندارد. سیگنال قیمتی دقیقاً جایی ضعیف است که بیشترین اثر را دارد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>مسئله</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>تعریف مسئله</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>اگر یارانهٔ گاز خانگی را هزینه‌ای عمومی بدانیم، پرسش سیاستی روشن است: این هزینه با چه دقتی به کسانی می‌رسد که واقعاً به آن نیاز دارند؟ داده‌های این گزارش پاسخ می‌دهند: نه با دقت زیاد. اقلیم تنها بخشی از مصرف مازاد را توضیح می‌دهد، پس نمی‌توان همهٔ آن را «نیاز اقلیمی موجه» دانست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>راهکار</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>شیب قیمتی پله‌های بالا را تندتر کنید  (کوتاه‌مدت · بالا)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>تندترکردن شیب در پله‌های بالای نردبان، دقیقاً همان اقلیتی را هدف می‌گیرد که بیشترین سهم مصرف مازاد را دارند، بدون آنکه به پله‌های کم‌مصرف فشار بیاورد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>راهکار</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>الگوی مصرف را اقلیمی کنید  (میان‌مدت · بالا)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>سقف الگو در استان سرد و گرم نباید یکی باشد. تعریف الگوی متناسب با دمای هر منطقه، مصرف موجه را از مصرف ناکارآمد جدا می‌کند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>راهکار</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>عایق‌بندی را جایی که مؤثر است تشویق کنید  (میان‌مدت · متوسط)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>استان‌هایی که بیش از آنچه دمایشان توجیه می‌کند مصرف دارند، بازدهی سرمایه‌گذاری در بهسازی ساختمان و تعویض وسایل گرمایشی در آن‌ها بیشترین است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>راهکار</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>صرفه‌جویی را به جیب مشترک برگردانید  (کوتاه‌مدت · متوسط)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>پاداش نقدی برای ماندن زیر الگو، سیگنال قیمتی را دوطرفه می‌کند: هم جریمهٔ پرمصرفی و هم پاداش کم‌مصرفی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>راهکار</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>شفافیت مصرف را به خود مشترک بدهید  (کوتاه‌مدت · متوسط)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>وقتی مشترک بداند در کدام پله است و تا سقف الگو چقدر فاصله دارد، رفتارش تغییر می‌کند. این ارزان‌ترین ابزار در کل فهرست است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>نتیجه‌گیری</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>نتیجه‌گیری</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>داده‌ها یک نکته را روشن می‌گویند: مسئلهٔ گاز خانگی ایران بیش از آنکه مسئلهٔ کمبود باشد، مسئلهٔ توزیع است. اکثریت بزرگی از مشترکین کم‌مصرف‌اند و اقلیتی کوچک سهم نامتناسبی از گاز و یارانهٔ پنهان را می‌برند. چون بخش مهمی از این مصرف مازاد را اقلیم توضیح نمی‌دهد، فضای واقعی برای سیاست‌گذاری وجود دارد — و اهرم اصلی، شیب تعرفه در پله‌های بالای نردبان است.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/downloads/gas-data-analysis-1404.xlsx
+++ b/downloads/gas-data-analysis-1404.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="شاخص‌ها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مصرف - دورهٔ سرد" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مشترکین - دورهٔ سرد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="دورهٔ گرم" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مصرف - دورهٔ گرم" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مشترکین - دورهٔ گرم" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="دورهٔ سرد" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="گروه‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="منحنی لورنز" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مقایسهٔ جهانی" sheetId="8" state="visible" r:id="rId8"/>
@@ -349,7 +349,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>منحنی لورنز مصرف گاز خانگی — کل کشور، دورهٔ سرد ۱۴۰۴</a:t>
+              <a:t>منحنی لورنز مصرف گاز خانگی — کل کشور، دورهٔ گرم ۱۴۰۴</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -984,7 +984,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>۳۱ استان · ۱۲ پلهٔ دورهٔ سرد · ۴ پلهٔ دورهٔ گرم</t>
+          <t>۳۱ استان · ۱۲ پلهٔ دورهٔ گرم · ۴ پلهٔ دورهٔ سرد</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>مصرف - دورهٔ سرد</t>
+          <t>مصرف - دورهٔ گرم</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>مشترکین - دورهٔ سرد</t>
+          <t>مشترکین - دورهٔ گرم</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>دورهٔ گرم</t>
+          <t>دورهٔ سرد</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>سرما فقط بخشی از ماجراست</t>
+          <t>اقلیم فقط بخشی از ماجراست</t>
         </is>
       </c>
       <c r="C4" s="22" t="inlineStr">
